--- a/NBFC-MF/Borrowers/Shantibala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Shantibala_Daily.xlsx
@@ -756,31 +756,33 @@
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="23" t="str">
+      <c r="A2" s="2">
+        <v>46242</v>
+      </c>
+      <c r="B2" s="23">
         <f>IF(A2&lt;&gt;"",1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="4">
         <f t="shared" ref="D2:D33" si="0">IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E2" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E2" s="4">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F2" s="4" t="str">
+        <v>93.087118407080297</v>
+      </c>
+      <c r="F2" s="4">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),D2-E2,"")</f>
-        <v/>
-      </c>
-      <c r="G2" s="4" t="str">
+        <v>206.91288159291969</v>
+      </c>
+      <c r="G2" s="4">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-F2,"")</f>
-        <v/>
-      </c>
-      <c r="H2" s="4" t="str">
+        <v>19793.087118407082</v>
+      </c>
+      <c r="H2" s="4">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-G2,"")</f>
-        <v/>
+        <v>206.91288159291798</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>17</v>
@@ -796,31 +798,33 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="24" t="str">
+      <c r="A3" s="19">
+        <v>46243</v>
+      </c>
+      <c r="B3" s="24">
         <f>IF(A3&lt;&gt;"",B2+1,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C3" s="20"/>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E3" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E3" s="21">
         <f t="shared" ref="E3:E34" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F3" s="21" t="str">
+        <v>92.124072211640794</v>
+      </c>
+      <c r="F3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="21" t="str">
+        <v>207.87592778835921</v>
+      </c>
+      <c r="G3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
-        <v/>
-      </c>
-      <c r="H3" s="21" t="str">
+        <v>19585.211190618724</v>
+      </c>
+      <c r="H3" s="21">
         <f t="shared" ref="H3:H34" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
-        <v/>
+        <v>414.78880938127622</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>10</v>
@@ -830,31 +834,33 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="23" t="str">
+      <c r="A4" s="2">
+        <v>46244</v>
+      </c>
+      <c r="B4" s="23">
         <f t="shared" ref="B4:B67" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="4" t="str">
+      <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E4" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="4" t="str">
+        <v>91.156543656439965</v>
+      </c>
+      <c r="F4" s="4">
         <f>IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="4" t="str">
+        <v>208.84345634356004</v>
+      </c>
+      <c r="G4" s="4">
         <f>IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="4" t="str">
+        <v>19376.367734275165</v>
+      </c>
+      <c r="H4" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>623.63226572483472</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>11</v>
@@ -862,31 +868,33 @@
       <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A5" s="19">
+        <v>46245</v>
+      </c>
+      <c r="B5" s="24">
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
+      <c r="D5" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E5" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
+        <v>90.184511878980132</v>
+      </c>
+      <c r="F5" s="21">
         <f>IF(AND($A5&lt;&gt;"",$B5&lt;&gt;""),D5-E5,"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
+        <v>209.81548812101988</v>
+      </c>
+      <c r="G5" s="21">
         <f>IF(AND($A5&lt;&gt;"",$B5&lt;&gt;""),G4-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
+        <v>19166.552246154144</v>
+      </c>
+      <c r="H5" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>833.44775384585591</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>12</v>
@@ -894,31 +902,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B6" s="23">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E6" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="4" t="str">
+        <v>89.207955919662083</v>
+      </c>
+      <c r="F6" s="4">
         <f>IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),D6-E6,"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="4" t="str">
+        <v>210.79204408033792</v>
+      </c>
+      <c r="G6" s="4">
         <f t="shared" ref="G6:G69" si="4">IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),G5-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="4" t="str">
+        <v>18955.760202073805</v>
+      </c>
+      <c r="H6" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1044.239797926195</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>13</v>
@@ -926,31 +936,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A7" s="19">
+        <v>46248</v>
+      </c>
+      <c r="B7" s="24">
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
+      <c r="D7" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E7" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+        <v>88.22685472133324</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" ref="F7:F70" si="5">IF(AND($A7&lt;&gt;"",$B7&lt;&gt;""),D7-E7,"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
+        <v>211.77314527866676</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="4"/>
+        <v>18743.987056795137</v>
+      </c>
+      <c r="H7" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1256.0129432048634</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>7</v>
@@ -960,31 +972,33 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A8" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B8" s="23">
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="4" t="str">
+      <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E8" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G8" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H8" s="4" t="str">
+        <v>87.241187128833474</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="5"/>
+        <v>212.75881287116653</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" si="4"/>
+        <v>18531.228243923972</v>
+      </c>
+      <c r="H8" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1468.7717560760284</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>14</v>
@@ -995,31 +1009,33 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A9" s="19">
+        <v>46251</v>
+      </c>
+      <c r="B9" s="24">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
+      <c r="D9" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E9" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
+        <v>86.250931888539071</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="5"/>
+        <v>213.74906811146093</v>
+      </c>
+      <c r="G9" s="21">
+        <f t="shared" si="4"/>
+        <v>18317.47917581251</v>
+      </c>
+      <c r="H9" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1682.5208241874898</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>8</v>
@@ -1029,31 +1045,33 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A10" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B10" s="23">
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E10" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G10" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H10" s="4" t="str">
+        <v>85.256067647904345</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="5"/>
+        <v>214.74393235209567</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="4"/>
+        <v>18102.735243460414</v>
+      </c>
+      <c r="H10" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1897.2647565395855</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>15</v>
@@ -1063,31 +1081,33 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A11" s="19">
+        <v>46255</v>
+      </c>
+      <c r="B11" s="24">
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
+      <c r="D11" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E11" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
+        <v>84.256572955001261</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="5"/>
+        <v>215.74342704499873</v>
+      </c>
+      <c r="G11" s="21">
+        <f t="shared" si="4"/>
+        <v>17886.991816415415</v>
+      </c>
+      <c r="H11" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2113.0081835845849</v>
       </c>
       <c r="J11" s="8"/>
       <c r="L11" s="22"/>
@@ -1124,7 +1144,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1159,7 +1179,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>24000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1194,7 +1214,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>24000</v>
+        <v>17886.991816415415</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1229,7 +1249,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>0</v>
+        <v>2113.0081835845849</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1262,9 +1282,9 @@
       <c r="J16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="16" t="str">
+      <c r="K16" s="16">
         <f>IF(A2,A2, "")</f>
-        <v/>
+        <v>46242</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1297,9 +1317,9 @@
       <c r="J17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="18" t="str">
+      <c r="K17" s="18">
         <f xml:space="preserve"> IF(A2,(K16 + 120),"")</f>
-        <v/>
+        <v>46362</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Shantibala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Shantibala_Daily.xlsx
@@ -1113,171 +1113,181 @@
       <c r="L11" s="22"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A12" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B12" s="23">
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E12" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G12" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H12" s="4" t="str">
+        <v>83.2524262580569</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="5"/>
+        <v>216.74757374194309</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="4"/>
+        <v>17670.244242673471</v>
+      </c>
+      <c r="H12" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2329.7557573265294</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46258</v>
+      </c>
+      <c r="B13" s="24">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
+      <c r="D13" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E13" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
+        <v>82.243605904988712</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="5"/>
+        <v>217.75639409501127</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="4"/>
+        <v>17452.487848578457</v>
+      </c>
+      <c r="H13" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2547.5121514215425</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>21</v>
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>21000</v>
+        <v>16200</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B14" s="23">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="4" t="str">
+      <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E14" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="str">
+        <v>81.230090142937655</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="5"/>
+        <v>218.76990985706234</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="4"/>
+        <v>17233.717938721395</v>
+      </c>
+      <c r="H14" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2766.2820612786054</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>22</v>
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>17886.991816415415</v>
+        <v>14295.302542559919</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="24">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
+      <c r="D15" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E15" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
+        <v>80.211857117799113</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="5"/>
+        <v>219.78814288220087</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="4"/>
+        <v>17013.929795839194</v>
+      </c>
+      <c r="H15" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2986.0702041608056</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>6</v>
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>2113.0081835845849</v>
+        <v>5704.6974574400811</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B16" s="23">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="4" t="str">
+      <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E16" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
+        <v>79.188884873751732</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="5"/>
+        <v>220.81111512624827</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="4"/>
+        <v>16793.118680712945</v>
+      </c>
+      <c r="H16" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3206.8813192870548</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -1288,31 +1298,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46264</v>
+      </c>
+      <c r="B17" s="24">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
+      <c r="D17" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E17" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
+        <v>78.161151352783904</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="5"/>
+        <v>221.83884864721608</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="4"/>
+        <v>16571.279832065728</v>
+      </c>
+      <c r="H17" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3428.7201679342725</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -1323,285 +1335,305 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B18" s="23">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4" t="str">
+      <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E18" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="str">
+        <v>77.12863439421821</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="5"/>
+        <v>222.87136560578179</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="4"/>
+        <v>16348.408466459945</v>
+      </c>
+      <c r="H18" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3651.591533540055</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A19" s="19">
+        <v>46267</v>
+      </c>
+      <c r="B19" s="24">
+        <f t="shared" si="3"/>
+        <v>18</v>
       </c>
       <c r="C19" s="20"/>
-      <c r="D19" s="21" t="str">
+      <c r="D19" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E19" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F19" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G19" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H19" s="21" t="str">
+        <v>76.091311734233543</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="5"/>
+        <v>223.90868826576644</v>
+      </c>
+      <c r="G19" s="21">
+        <f t="shared" si="4"/>
+        <v>16124.499778194178</v>
+      </c>
+      <c r="H19" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3875.5002218058216</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A20" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B20" s="23">
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="4" t="str">
+      <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E20" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E20" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G20" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="str">
+        <v>75.049161005385074</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="5"/>
+        <v>224.95083899461491</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="4"/>
+        <v>15899.548939199563</v>
+      </c>
+      <c r="H20" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4100.4510608004366</v>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A21" s="19">
+        <v>46269</v>
+      </c>
+      <c r="B21" s="24">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="21" t="str">
+      <c r="D21" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E21" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H21" s="21" t="str">
+        <v>74.002159736121882</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="5"/>
+        <v>225.99784026387812</v>
+      </c>
+      <c r="G21" s="21">
+        <f t="shared" si="4"/>
+        <v>15673.551098935684</v>
+      </c>
+      <c r="H21" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4326.4489010643156</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A22" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B22" s="23">
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="4" t="str">
+      <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E22" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E22" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G22" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="str">
+        <v>72.95028535030248</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="5"/>
+        <v>227.04971464969753</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="4"/>
+        <v>15446.501384285986</v>
+      </c>
+      <c r="H22" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4553.4986157140138</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A23" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B23" s="24">
+        <f t="shared" si="3"/>
+        <v>22</v>
       </c>
       <c r="C23" s="20"/>
-      <c r="D23" s="21" t="str">
+      <c r="D23" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E23" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E23" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F23" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G23" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H23" s="21" t="str">
+        <v>71.893515166707971</v>
+      </c>
+      <c r="F23" s="21">
+        <f t="shared" si="5"/>
+        <v>228.10648483329203</v>
+      </c>
+      <c r="G23" s="21">
+        <f t="shared" si="4"/>
+        <v>15218.394899452695</v>
+      </c>
+      <c r="H23" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4781.6051005473055</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A24" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B24" s="23">
+        <f t="shared" si="3"/>
+        <v>23</v>
       </c>
       <c r="C24" s="3"/>
-      <c r="D24" s="4" t="str">
+      <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E24" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E24" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F24" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H24" s="4" t="str">
+        <v>70.831826398552991</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="5"/>
+        <v>229.16817360144699</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="4"/>
+        <v>14989.226725851247</v>
+      </c>
+      <c r="H24" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5010.7732741487525</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A25" s="19">
+        <v>46273</v>
+      </c>
+      <c r="B25" s="24">
+        <f t="shared" si="3"/>
+        <v>24</v>
       </c>
       <c r="C25" s="20"/>
-      <c r="D25" s="21" t="str">
+      <c r="D25" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E25" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E25" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F25" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G25" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H25" s="21" t="str">
+        <v>69.765196152994378</v>
+      </c>
+      <c r="F25" s="21">
+        <f t="shared" si="5"/>
+        <v>230.23480384700562</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="4"/>
+        <v>14758.991922004241</v>
+      </c>
+      <c r="H25" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5241.0080779957589</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A26" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B26" s="23">
+        <f t="shared" si="3"/>
+        <v>25</v>
       </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="4" t="str">
+      <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E26" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E26" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G26" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H26" s="4" t="str">
+        <v>68.693601430637528</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="5"/>
+        <v>231.30639856936247</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="4"/>
+        <v>14527.685523434879</v>
+      </c>
+      <c r="H26" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5472.3144765651214</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A27" s="19">
+        <v>46275</v>
+      </c>
+      <c r="B27" s="24">
+        <f t="shared" si="3"/>
+        <v>26</v>
       </c>
       <c r="C27" s="20"/>
-      <c r="D27" s="21" t="str">
+      <c r="D27" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E27" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E27" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F27" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G27" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H27" s="21" t="str">
+        <v>67.617019125040443</v>
+      </c>
+      <c r="F27" s="21">
+        <f t="shared" si="5"/>
+        <v>232.38298087495957</v>
+      </c>
+      <c r="G27" s="21">
+        <f t="shared" si="4"/>
+        <v>14295.302542559919</v>
+      </c>
+      <c r="H27" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5704.6974574400811</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
